--- a/src/test/excel/testdata.xlsx
+++ b/src/test/excel/testdata.xlsx
@@ -2,19 +2,22 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\seleniumTesting\POMTestExecution\src\test\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2e9f1ff2b390a8ed/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAD526EF-26F8-446D-BC41-DF635837059B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8AA40D74-FBF8-43C4-BF65-6AB151AFCFD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="38700" windowHeight="15345" xr2:uid="{D68EBB81-B61C-4DDA-9343-37D6858EAB7B}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="38700" windowHeight="15345" activeTab="4" xr2:uid="{5646E030-7350-4DC6-A18A-3CD70EBE5421}"/>
   </bookViews>
   <sheets>
-    <sheet name="findNewCar" sheetId="6" r:id="rId1"/>
-    <sheet name="carNameAndPrice" sheetId="7" r:id="rId2"/>
+    <sheet name="itemsPresent" sheetId="1" r:id="rId1"/>
+    <sheet name="printAll" sheetId="2" r:id="rId2"/>
+    <sheet name="search" sheetId="3" r:id="rId3"/>
+    <sheet name="priceCompare" sheetId="4" r:id="rId4"/>
+    <sheet name="requestValidation" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -24,51 +27,46 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="8">
+  <si>
+    <t>runMode</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
   <si>
     <t>browser</t>
   </si>
   <si>
+    <t>searchItem</t>
+  </si>
+  <si>
     <t>chrome</t>
   </si>
   <si>
-    <t>runmode</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>carBrand</t>
-  </si>
-  <si>
-    <t>Hyundai</t>
-  </si>
-  <si>
-    <t>BMW</t>
-  </si>
-  <si>
-    <t>Toyota</t>
-  </si>
-  <si>
-    <t>carTitle</t>
-  </si>
-  <si>
-    <t>Hyundai Cars</t>
-  </si>
-  <si>
-    <t>BMW Cars</t>
-  </si>
-  <si>
-    <t>Toyota Cars</t>
+    <t>Visual Studio Professional 2026</t>
+  </si>
+  <si>
+    <t>firefox</t>
   </si>
 </sst>
 </file>
@@ -79,7 +77,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -124,9 +122,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -134,39 +132,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -218,7 +216,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -270,7 +268,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -329,13 +327,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -344,6 +335,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -408,75 +406,71 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B19CC20-CA68-408E-82BB-EF86F156B98E}">
-  <dimension ref="A1:D4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDF38ECD-EADE-4AF2-B9B9-016E82F821E7}">
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
       <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" t="s">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -485,64 +479,173 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D96160C7-E404-4AF2-827F-3E46D55D512F}">
-  <dimension ref="A1:D4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1A42EFE-7680-4BF5-8A69-9A0A2A6AE0A1}">
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
       <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92D0EEA4-AF07-4561-8770-6B48CE353D5A}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
       <c r="C4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03418D79-598A-4054-AD92-42C7D86A5862}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{492932F9-B447-4EEF-BB00-3B9D10CF3A78}">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
